--- a/build/temp/pages/StructureDefinition-cibmtr-patient.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-patient.xlsx
@@ -6622,7 +6622,7 @@
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>52</v>

--- a/build/temp/pages/StructureDefinition-cibmtr-patient.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T07:35:08-05:00</t>
+    <t>2026-06-11T12:11:14-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/temp/pages/StructureDefinition-cibmtr-patient.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T12:11:14-05:00</t>
+    <t>2026-06-12T09:38:46-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/temp/pages/StructureDefinition-cibmtr-patient.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T09:38:46-05:00</t>
+    <t>2026-06-21T22:38:39-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/temp/pages/StructureDefinition-cibmtr-patient.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T22:38:39-05:00</t>
+    <t>2026-06-21T23:16:04-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/temp/pages/StructureDefinition-cibmtr-patient.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-patient.xlsx
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T23:16:04-05:00</t>
+    <t>2026-06-22T08:51:47-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program</t>
+    <t>The Medical College of Wisconsin, Inc. and the NMDP</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program (http://www.cibmtr.org)</t>
+    <t>The Medical College of Wisconsin, Inc. and the NMDP (http://www.cibmtr.org)</t>
   </si>
   <si>
     <t>Bob Milius (bmilius@nmdp.org)</t>

--- a/build/temp/pages/StructureDefinition-cibmtr-patient.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-patient.xlsx
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:51:47-05:00</t>
+    <t>2026-06-22T09:21:59-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the NMDP</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the NMDP (http://www.cibmtr.org)</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP (http://www.cibmtr.org)</t>
   </si>
   <si>
     <t>Bob Milius (bmilius@nmdp.org)</t>

--- a/build/temp/pages/StructureDefinition-cibmtr-patient.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:21:59-05:00</t>
+    <t>2026-06-25T19:24:07-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/temp/pages/StructureDefinition-cibmtr-patient.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T19:24:07-05:00</t>
+    <t>2026-08-19T10:07:56-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -707,7 +707,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -790,7 +790,7 @@
     <t>𝗔𝗗𝗗𝗜𝗧𝗜𝗢𝗡𝗔𝗟 𝗨𝗦𝗖𝗗𝗜: US Core Race Extension. (multiple races are supported in the extension)</t>
   </si>
   <si>
-    <t>Concepts classifying the person into a named category of humans sharing common history, traits, geographical origin or nationality.  The race codes used to represent these concepts are based upon the [CDC Race and Ethnicity Code Set Version 1.0](http://www.cdc.gov/phin/resources/vocabulary/index.html) which includes over 900 concepts for representing race and ethnicity of which 921 reference race.  The race concepts are grouped by and pre-mapped to the 5 OMB race categories:
+    <t>Concepts classifying the person into a named category of humans sharing common history, traits, geographical origin or nationality.  The race codes used to represent these concepts are based upon the [Race &amp; Ethnicity - CDC (CDCREC)](https://phinvads.cdc.gov/vads/ViewCodeSystem.action?id=2.16.840.1.113883.6.238) code system. Detailed race concepts are grouped by and pre-mapped to the 5 OMB race categories:
    - American Indian or Alaska Native
    - Asian
    - Black or African American
@@ -819,7 +819,9 @@
     <t>𝗔𝗗𝗗𝗜𝗧𝗜𝗢𝗡𝗔𝗟 𝗨𝗦𝗖𝗗𝗜: US Core ethnicity Extension (multiple ethnicities are supported in the extension)</t>
   </si>
   <si>
-    <t>Concepts classifying the person into a named category of humans sharing common history, traits, geographical origin or nationality.  The ethnicity codes used to represent these concepts are based upon the [CDC ethnicity and Ethnicity Code Set Version 1.0](http://www.cdc.gov/phin/resources/vocabulary/index.html) which includes over 900 concepts for representing race and ethnicity of which 43 reference ethnicity.  The ethnicity concepts are grouped by and pre-mapped to the 2 OMB ethnicity categories: - Hispanic or Latino - Not Hispanic or Latino.</t>
+    <t>Concepts classifying the person into a named category of humans sharing common history, traits, geographical origin or nationality.  The ethnicity codes used to represent these concepts are based upon the [Race &amp; Ethnicity - CDC (CDCREC)](https://phinvads.cdc.gov/vads/ViewCodeSystem.action?id=2.16.840.1.113883.6.238) code system. Detailed ethnicity concepts are grouped by and pre-mapped to the 2 OMB ethnicity categories:
+   - Hispanic or Latino
+   - Not Hispanic or Latino.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -848,14 +850,14 @@
     <t>sex</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/us/core/StructureDefinition/us-core-sex}
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/us/core/StructureDefinition/us-core-individual-sex}
 </t>
   </si>
   <si>
     <t>𝗔𝗗𝗗𝗜𝗧𝗜𝗢𝗡𝗔𝗟 𝗨𝗦𝗖𝗗𝗜: Sex Extension</t>
   </si>
   <si>
-    <t>The US Core Sex Extension is used to reflect the documentation of a person's sex. It aligns with the C-CDA Sex Observation (LOINC 46098-0).</t>
+    <t>The US Core Individual Sex Extension is used to reflect the documentation of a person's sex. It aligns with the C-CDA Sex Observation (LOINC 46098-0).</t>
   </si>
   <si>
     <t>Patient.extension:interpreterRequired</t>
@@ -1020,7 +1022,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1105,7 +1107,7 @@
     <t>Patient.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -2165,7 +2167,7 @@
     <t>The domestic partnership status of a person.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/marital-status</t>
+    <t>http://hl7.org/fhir/ValueSet/marital-status|4.0.1</t>
   </si>
   <si>
     <t>player[classCode=PSN]/maritalStatusCode</t>
@@ -2294,7 +2296,7 @@
     <t>The nature of the relationship between a patient and a contact person for that patient.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship</t>
+    <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship|4.0.1</t>
   </si>
   <si>
     <t>code</t>
@@ -2482,7 +2484,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Organization|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -2553,7 +2555,7 @@
     <t>Patient.link.other</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -2932,7 +2934,7 @@
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="85.89453125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="46.88671875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.0234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
